--- a/data-raw/metadata/yuba_metadata.xlsx
+++ b/data-raw/metadata/yuba_metadata.xlsx
@@ -1057,7 +1057,7 @@
         <v>36489</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>45835</v>
+        <v>46126</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/metadata/yuba_metadata.xlsx
+++ b/data-raw/metadata/yuba_metadata.xlsx
@@ -1057,7 +1057,7 @@
         <v>36489</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46126</v>
+        <v>46191</v>
       </c>
     </row>
   </sheetData>
